--- a/data/DDI_types.xlsx
+++ b/data/DDI_types.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28215" windowHeight="12420"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -370,368 +370,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -740,309 +404,42 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  </cellStyleXfs>
+  <cellXfs count="6">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1053,10 +450,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1083,82 +480,82 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1170,1417 +567,1446 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:C115"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.125" customWidth="1"/>
-    <col min="3" max="3" width="23.75" customWidth="1"/>
+    <col min="1" max="1" style="4" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="51.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="23.719285714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18" hidden="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18" hidden="1">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18" hidden="1">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18" hidden="1">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18" hidden="1">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18" hidden="1">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18" hidden="1">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18" hidden="1">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18" hidden="1">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18" hidden="1">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18" hidden="1">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18" hidden="1">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18" hidden="1">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18" hidden="1">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18" hidden="1">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18" hidden="1">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18" hidden="1">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18" hidden="1">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18" hidden="1">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18" hidden="1">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18" hidden="1">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18" hidden="1">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18" hidden="1">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18" hidden="1">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18" hidden="1">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18" hidden="1">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18" hidden="1">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18" hidden="1">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18" hidden="1">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18" hidden="1">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18" hidden="1">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18" hidden="1">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18" hidden="1">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18" hidden="1">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18" hidden="1">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18" hidden="1">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="3">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18" hidden="1">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18" hidden="1">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18" hidden="1">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18" hidden="1">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18" hidden="1">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18" hidden="1">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="3">
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18" hidden="1">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18" hidden="1">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18" hidden="1">
+      <c r="A51" s="3">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18" hidden="1">
+      <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18" hidden="1">
+      <c r="A53" s="3">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="3">
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18" hidden="1">
+      <c r="A54" s="3">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18" hidden="1">
+      <c r="A55" s="3">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18" hidden="1">
+      <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18" hidden="1">
+      <c r="A57" s="3">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18" hidden="1">
+      <c r="A58" s="3">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18" hidden="1">
+      <c r="A59" s="3">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18" hidden="1">
+      <c r="A60" s="3">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18" hidden="1">
+      <c r="A61" s="3">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18">
+      <c r="A62" s="3">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18" hidden="1">
+      <c r="A63" s="3">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18" hidden="1">
+      <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18" hidden="1">
+      <c r="A65" s="3">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18" hidden="1">
+      <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18" hidden="1">
+      <c r="A67" s="3">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18" hidden="1">
+      <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18" hidden="1">
+      <c r="A69" s="3">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="3">
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18" hidden="1">
+      <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18" hidden="1">
+      <c r="A71" s="3">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18" hidden="1">
+      <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="3">
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18" hidden="1">
+      <c r="A73" s="3">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18" hidden="1">
+      <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18" hidden="1">
+      <c r="A75" s="3">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18" hidden="1">
+      <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18" hidden="1">
+      <c r="A77" s="3">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18" hidden="1">
+      <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18" hidden="1">
+      <c r="A79" s="3">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18" hidden="1">
+      <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18" hidden="1">
+      <c r="A81" s="3">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18" hidden="1">
+      <c r="A82" s="3">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="3">
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18" hidden="1">
+      <c r="A83" s="3">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18">
+      <c r="A84" s="3">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18" hidden="1">
+      <c r="A85" s="3">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18" hidden="1">
+      <c r="A86" s="3">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18" hidden="1">
+      <c r="A87" s="3">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18" hidden="1">
+      <c r="A88" s="3">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18" hidden="1">
+      <c r="A89" s="3">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18" hidden="1">
+      <c r="A90" s="3">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18" hidden="1">
+      <c r="A91" s="3">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18" hidden="1">
+      <c r="A92" s="3">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18" hidden="1">
+      <c r="A93" s="3">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18" hidden="1">
+      <c r="A94" s="3">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18" hidden="1">
+      <c r="A95" s="3">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18" hidden="1">
+      <c r="A96" s="3">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
-      <c r="A97">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18" hidden="1">
+      <c r="A97" s="3">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
-      <c r="A98">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18" hidden="1">
+      <c r="A98" s="3">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
-      <c r="A99">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18" hidden="1">
+      <c r="A99" s="3">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
-      <c r="A100">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18" hidden="1">
+      <c r="A100" s="3">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
-      <c r="A101">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18" hidden="1">
+      <c r="A101" s="3">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
-      <c r="A102">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18" hidden="1">
+      <c r="A102" s="3">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
-      <c r="A103">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18" hidden="1">
+      <c r="A103" s="3">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
-      <c r="A104">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18">
+      <c r="A104" s="3">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
-      <c r="A105">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18" hidden="1">
+      <c r="A105" s="3">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
-      <c r="A106">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18" hidden="1">
+      <c r="A106" s="3">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
-      <c r="A107">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18" hidden="1">
+      <c r="A107" s="3">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
-      <c r="A108">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18">
+      <c r="A108" s="3">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
-      <c r="A109">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18" hidden="1">
+      <c r="A109" s="3">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
-      <c r="A110">
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18" hidden="1">
+      <c r="A110" s="3">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
-      <c r="A111">
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18" hidden="1">
+      <c r="A111" s="3">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
-      <c r="A112">
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18" hidden="1">
+      <c r="A112" s="3">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
-      <c r="A113">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18" hidden="1">
+      <c r="A113" s="3">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114">
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18" hidden="1">
+      <c r="A114" s="3">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18" hidden="1">
+      <c r="A115" s="3">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="3">
         <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>